--- a/05_finance/Финансовая_модель_ИНГОССЕМЬЯ.xlsx
+++ b/05_finance/Финансовая_модель_ИНГОССЕМЬЯ.xlsx
@@ -1461,7 +1461,7 @@
     <t xml:space="preserve">Чувствительность NPV до налога за 60 мес. к параметрам (базовый сценарий)</t>
   </si>
   <si>
-    <t xml:space="preserve">Результаты получены многократным прогоном модели в model.py (каждая строка требует отдельного пересчета всех 60 месяцев), поэтому перенесены значениями. Пересчет: python model.py.</t>
+    <t xml:space="preserve">Результаты получены многократным прогоном модели (каждая строка требует отдельного пересчета всех 60 месяцев), поэтому перенесены значениями.</t>
   </si>
   <si>
     <t xml:space="preserve">NPV базового сценария, руб.</t>
